--- a/Bajaj Mapping.xlsx
+++ b/Bajaj Mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityakumar/Downloads/Ather/Ather 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityakumar/Downloads/Bajaj/cps-lead-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20A56DB-B9AB-2946-8D17-68ABD51A177C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC2B0FC-498B-B54D-8136-2691B51F1AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16180" xr2:uid="{9042D7FF-378F-0C4B-A817-B24004E25046}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="71">
   <si>
     <t>Bajaj</t>
   </si>
@@ -231,6 +231,27 @@
   </si>
   <si>
     <t>Model Name</t>
+  </si>
+  <si>
+    <t>Bajaj Chetak 2903</t>
+  </si>
+  <si>
+    <t>Bajaj Chetak C2501</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar N150</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar 180</t>
+  </si>
+  <si>
+    <t>Bajaj WEGO P9018</t>
+  </si>
+  <si>
+    <t>Bajaj WEGO P70</t>
+  </si>
+  <si>
+    <t>Bajaj WEGO C90</t>
   </si>
 </sst>
 </file>
@@ -642,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A6C1A8-F9DF-DF4E-9D31-E1A661CB5774}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -1255,6 +1276,83 @@
         <v>61</v>
       </c>
     </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Bajaj Mapping.xlsx
+++ b/Bajaj Mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityakumar/Downloads/Bajaj/cps-lead-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC2B0FC-498B-B54D-8136-2691B51F1AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5DE7CC-8999-5944-9A8E-08F46CA3D2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16180" xr2:uid="{9042D7FF-378F-0C4B-A817-B24004E25046}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="86">
   <si>
     <t>Bajaj</t>
   </si>
@@ -252,6 +252,51 @@
   </si>
   <si>
     <t>Bajaj WEGO C90</t>
+  </si>
+  <si>
+    <t>Jawa</t>
+  </si>
+  <si>
+    <t>Jawa 42 Bobber</t>
+  </si>
+  <si>
+    <t>Yezdi</t>
+  </si>
+  <si>
+    <t>Jawa 350</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>Jawa 42 FJ</t>
+  </si>
+  <si>
+    <t>Yezdi Scrambler</t>
+  </si>
+  <si>
+    <t>Jawa 42</t>
+  </si>
+  <si>
+    <t>Jawa Perak</t>
+  </si>
+  <si>
+    <t>Yezdi Roadster</t>
+  </si>
+  <si>
+    <t>Yezdi Adventure</t>
+  </si>
+  <si>
+    <t>Yezdi Scrambler 350</t>
+  </si>
+  <si>
+    <t>BSA Scrambler 650</t>
+  </si>
+  <si>
+    <t>BSA Gold Star</t>
+  </si>
+  <si>
+    <t>2024 Yezdi Adventure</t>
   </si>
 </sst>
 </file>
@@ -663,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A6C1A8-F9DF-DF4E-9D31-E1A661CB5774}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -1353,6 +1398,138 @@
         <v>70</v>
       </c>
     </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
